--- a/Required Data Dictionary.xlsx
+++ b/Required Data Dictionary.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ling1\Documents\USDA APHIS 2\PIS Gitlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C110F03-3E04-40EE-B800-E741AFC33FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1CD24-BB72-432D-ABB8-C202D55FD4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5DB53C8F-50D8-4CF8-BD88-2B5F353578DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5DB53C8F-50D8-4CF8-BD88-2B5F353578DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Required_Columns_for_Main_Input" sheetId="1" r:id="rId1"/>
+    <sheet name="Output Data Dictionary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="130">
   <si>
     <t>Data Field Name</t>
   </si>
@@ -2022,4 +2023,43 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DC9D0E-3B70-4A1D-BCC4-A182A79A7BA4}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Required Data Dictionary.xlsx
+++ b/Required Data Dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ling1\Documents\USDA APHIS 2\PIS Gitlab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agorjk1\PycharmProjects\plant-inspection-station-simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D1CD24-BB72-432D-ABB8-C202D55FD4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4D6F87-61FA-4D99-9942-8C293E5BCAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5DB53C8F-50D8-4CF8-BD88-2B5F353578DB}"/>
+    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{5DB53C8F-50D8-4CF8-BD88-2B5F353578DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Required_Columns_for_Main_Input" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="83">
   <si>
     <t>Data Field Name</t>
   </si>
@@ -184,165 +184,21 @@
     <t>Important to note that this is an approximated value that is inferred from the TOTAL_SAMPLING_UNITS_FOR_RISK_UNIT and QUANTITY variables (proportioning out the TOTAL_SAMPLING_UNITS_FOR_RISK_UNIT based on QUANTITY).</t>
   </si>
   <si>
-    <t>FROM RAW DATA</t>
-  </si>
-  <si>
     <t>Calculated/Merged (Not in Original Inspection Data)</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>OPTIONAL</t>
-  </si>
-  <si>
     <t>Optional/Required (specify for which modules)</t>
   </si>
   <si>
-    <t>comm_ID</t>
-  </si>
-  <si>
-    <t>INSPECTION_ID</t>
-  </si>
-  <si>
-    <t>REF_COMMODITY_ID</t>
-  </si>
-  <si>
-    <t>CERTIFIED_FACILITY_NAME</t>
-  </si>
-  <si>
-    <t>CERTIFIED_FACILITY_NUMBER</t>
-  </si>
-  <si>
-    <t>COMMODITY_CLASSIFICATION</t>
-  </si>
-  <si>
-    <t>COMMODITY_TAXONOMIC_DISPLAY_NAME</t>
-  </si>
-  <si>
-    <t>COMMODITY_HOST_TYPE</t>
-  </si>
-  <si>
-    <t>COMMODITY_TYPE</t>
-  </si>
-  <si>
-    <t>CONSIGNEE_NAME</t>
-  </si>
-  <si>
-    <t>DESTINATION_STATE_NAME</t>
-  </si>
-  <si>
-    <t>DISPOSITION_CODE</t>
-  </si>
-  <si>
-    <t>ENTRY_NUMBER</t>
-  </si>
-  <si>
-    <t>ENTRY_LINE_NUMBER</t>
-  </si>
-  <si>
-    <t>PGA_LINE_NUMBER</t>
-  </si>
-  <si>
-    <t>PRODUCER_ID</t>
-  </si>
-  <si>
-    <t>QUANTITY_UNITS_NAME</t>
-  </si>
-  <si>
-    <t>WADS_CODE</t>
-  </si>
-  <si>
-    <t>SAMPLING_UNITS</t>
-  </si>
-  <si>
-    <t>IS_RBS</t>
-  </si>
-  <si>
-    <t>RBS_STATUS</t>
-  </si>
-  <si>
-    <t>GROWING_MEDIA_PRESENCE</t>
-  </si>
-  <si>
-    <t>CREATED_DATETIME</t>
-  </si>
-  <si>
-    <t>INSPECTION_DATETIME</t>
-  </si>
-  <si>
-    <t>CATEGORY</t>
-  </si>
-  <si>
-    <t>SUBCATEGORY</t>
-  </si>
-  <si>
-    <t>INSPECTION_LOCATION_ID</t>
-  </si>
-  <si>
-    <t>PATHWAY_ID</t>
-  </si>
-  <si>
-    <t>INSPECTION_LOCATION_STATE_CODE</t>
-  </si>
-  <si>
-    <t>DOCUMENT_REVIEW_OVERTIME_ID</t>
-  </si>
-  <si>
-    <t>DOCUMENT_REVIEW_OVERTIME_NAME</t>
-  </si>
-  <si>
-    <t>INSPECTION_RESULTS_OVERTIME_ID</t>
-  </si>
-  <si>
-    <t>INSPECTION_RESULTS_OVERTIME_NAME</t>
-  </si>
-  <si>
-    <t>OFFSHORE_CUT_SHIP_INSP_NEEDED</t>
-  </si>
-  <si>
-    <t>TAXONOMY_SUBSPECIES</t>
-  </si>
-  <si>
-    <t>MODE_OF_TRANSPORT</t>
-  </si>
-  <si>
-    <t>inspection</t>
-  </si>
-  <si>
-    <t>shipment</t>
-  </si>
-  <si>
-    <t>fiscal_year</t>
-  </si>
-  <si>
-    <t>calendar_year</t>
-  </si>
-  <si>
-    <t>HOST_PROXIMITY_ID</t>
-  </si>
-  <si>
-    <t>HOST_PROXIMITY</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>month</t>
-  </si>
-  <si>
-    <t>Total_Sampling_Units_for_Risk_Unit</t>
-  </si>
-  <si>
     <t>Required (consignment)</t>
   </si>
   <si>
     <t>Required (consignment, contamination)</t>
   </si>
   <si>
-    <t>Port-of-entry where the inspection occurred</t>
-  </si>
-  <si>
     <t>The originating country of shipment</t>
   </si>
   <si>
@@ -428,6 +284,9 @@
   </si>
   <si>
     <t>Dryopteris wallichiana - Dryopteris wallichiana</t>
+  </si>
+  <si>
+    <t>Plant inspection station where the inspection occurred</t>
   </si>
 </sst>
 </file>
@@ -832,25 +691,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD678CC-596C-4916-AE72-B51060BEEAA0}">
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="72.7109375" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="42.6640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="72.6640625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -862,18 +721,18 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>18</v>
@@ -885,18 +744,18 @@
         <v>43</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>19</v>
@@ -914,12 +773,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
@@ -931,18 +790,18 @@
         <v>1</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>20</v>
@@ -960,12 +819,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>46</v>
@@ -983,12 +842,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
@@ -1006,12 +865,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>21</v>
@@ -1023,1001 +882,326 @@
         <v>2400</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>127</v>
+        <v>79</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2028,23 +1212,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DC9D0E-3B70-4A1D-BCC4-A182A79A7BA4}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.28515625" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>

--- a/Required Data Dictionary.xlsx
+++ b/Required Data Dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agorjk1\PycharmProjects\plant-inspection-station-simulation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ling1\Documents\USDA APHIS 2\PIS Gitlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4D6F87-61FA-4D99-9942-8C293E5BCAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5F7BE5-ACE4-4282-AF87-E6312AB381FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3255" windowWidth="29040" windowHeight="15720" xr2:uid="{5DB53C8F-50D8-4CF8-BD88-2B5F353578DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5DB53C8F-50D8-4CF8-BD88-2B5F353578DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Required_Columns_for_Main_Input" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="161">
   <si>
     <t>Data Field Name</t>
   </si>
@@ -287,6 +287,240 @@
   </si>
   <si>
     <t>Plant inspection station where the inspection occurred</t>
+  </si>
+  <si>
+    <t>Scenarios</t>
+  </si>
+  <si>
+    <t>Number of Scenarios in experiment</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Run Summary</t>
+  </si>
+  <si>
+    <t>Replications per scenario</t>
+  </si>
+  <si>
+    <t>Number of replication runs that were simulated in each scenario</t>
+  </si>
+  <si>
+    <t>Numeric</t>
+  </si>
+  <si>
+    <t>Replication rows</t>
+  </si>
+  <si>
+    <t>Number of rows corresponding to replication</t>
+  </si>
+  <si>
+    <t>Inpsected Consignments</t>
+  </si>
+  <si>
+    <t>Number of consignments inspected in each replication</t>
+  </si>
+  <si>
+    <t>Total shipments run</t>
+  </si>
+  <si>
+    <t>Estimated total consignments processed across all scenarios and replications.</t>
+  </si>
+  <si>
+    <t>Consignments and shipments used interchangeably</t>
+  </si>
+  <si>
+    <t>Consignment-level Slippage</t>
+  </si>
+  <si>
+    <t>Inspection-level Slippage</t>
+  </si>
+  <si>
+    <t>Sample-level Slippage</t>
+  </si>
+  <si>
+    <t>Slippage Level</t>
+  </si>
+  <si>
+    <t>Total slipped plant units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average number of slipped plant units among replications summed across scenarios </t>
+  </si>
+  <si>
+    <t>Number of contaminated consignments not detected during inspection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of contaminated inspections not detected during inspection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of contaminated samples not detected during inspection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of contaminated plants not detected during inspection </t>
+  </si>
+  <si>
+    <t>Action level</t>
+  </si>
+  <si>
+    <t>Consignment-level Slippage %</t>
+  </si>
+  <si>
+    <t>Inspection-level Slippage %</t>
+  </si>
+  <si>
+    <t>Sample-level Slippage %</t>
+  </si>
+  <si>
+    <t>Plant-level Slippage %</t>
+  </si>
+  <si>
+    <t>Percent of slipped consignments over the total number of contaminated consignments</t>
+  </si>
+  <si>
+    <t>Percent of slipped inspection units over the total number of contaminated inpsection units</t>
+  </si>
+  <si>
+    <t>Percent of slipped sample units over the total number of contaminated sample units</t>
+  </si>
+  <si>
+    <t>Percent of slipped plant units over the total number of contaminated plant units</t>
+  </si>
+  <si>
+    <t>Number of detected consignments where action was taken</t>
+  </si>
+  <si>
+    <t>Number of detected inspection units where action was taken</t>
+  </si>
+  <si>
+    <t>Number of detected sample units where action was taken</t>
+  </si>
+  <si>
+    <t>Number of detected plant units where action was taken</t>
+  </si>
+  <si>
+    <t>Contamination level</t>
+  </si>
+  <si>
+    <t>Contaminated Consignments</t>
+  </si>
+  <si>
+    <t>Number of consignments contaminated with pests</t>
+  </si>
+  <si>
+    <t>Number of inspection units contaminated with pests</t>
+  </si>
+  <si>
+    <t>Number of sample units contaminated with pests</t>
+  </si>
+  <si>
+    <t>Number of plant units contaminated with pests</t>
+  </si>
+  <si>
+    <t>In the word document output, mean value across replications is reported for each scenario</t>
+  </si>
+  <si>
+    <t>Contaminated Consignments %</t>
+  </si>
+  <si>
+    <t>Inspection Workload Level</t>
+  </si>
+  <si>
+    <t>Consignments-level Intercepts</t>
+  </si>
+  <si>
+    <t>Inspection-level Intercepts</t>
+  </si>
+  <si>
+    <t>Sample-level Intercepts</t>
+  </si>
+  <si>
+    <t>Plant-level Intercepts</t>
+  </si>
+  <si>
+    <t>Inspection-level inspected</t>
+  </si>
+  <si>
+    <t>Consignment-level inspected</t>
+  </si>
+  <si>
+    <t>Sample-level inspected</t>
+  </si>
+  <si>
+    <t>Plant-level inspected</t>
+  </si>
+  <si>
+    <t>Percent of contaminated consignments of all consignments</t>
+  </si>
+  <si>
+    <t>Percent of contaminated inspection units  of all inspection units</t>
+  </si>
+  <si>
+    <t>Percent of contaminated sample units of all sample units</t>
+  </si>
+  <si>
+    <t>Percent of contaminated plant units of all plant units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of consignments selected for inpsection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of inspection units selected for inpsection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of sample units selected for inpsection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of plant units selected for inpsection </t>
+  </si>
+  <si>
+    <t>Consignment-level inspected %</t>
+  </si>
+  <si>
+    <t>Percent of consignments inspected of all consignments</t>
+  </si>
+  <si>
+    <t>Percent of inspection units inspected of all inspections</t>
+  </si>
+  <si>
+    <t>Percent of sample units inspected of all samples</t>
+  </si>
+  <si>
+    <t>Percent of plant units inspected of all plants</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>Plant-level Slippage / Mean slipped plant units</t>
+  </si>
+  <si>
+    <t>Contaminated Inpsection / Inspection unit contaminated mean</t>
+  </si>
+  <si>
+    <t>Contaminated Samples / Sample unit contaminated mean</t>
+  </si>
+  <si>
+    <t>Contaminated Plants % / Plant contamination %</t>
+  </si>
+  <si>
+    <t>Contaminated Samples % / Sample unit contamination %</t>
+  </si>
+  <si>
+    <t>Contaminated Plants / Plant contaminated mean</t>
+  </si>
+  <si>
+    <t>Contaminated Inpsection % / Inspection unit contamination %</t>
+  </si>
+  <si>
+    <t>Plant-level inspected % / Plant units inspected %</t>
+  </si>
+  <si>
+    <t>Sample-level inspected % / Sample units inspected %</t>
+  </si>
+  <si>
+    <t>Inspection-level inspected % / Inspection units inspected %</t>
   </si>
 </sst>
 </file>
@@ -351,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -376,6 +610,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,19 +935,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD678CC-596C-4916-AE72-B51060BEEAA0}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="37.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="72.6640625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="42.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="41.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="72.7109375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -727,7 +970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>36</v>
       </c>
@@ -750,7 +993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -773,7 +1016,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -796,7 +1039,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -819,7 +1062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
@@ -842,7 +1085,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -865,7 +1108,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -888,7 +1131,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
@@ -909,7 +1152,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -930,7 +1173,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -951,7 +1194,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
@@ -972,7 +1215,7 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>23</v>
       </c>
@@ -993,7 +1236,7 @@
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1014,7 +1257,7 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
@@ -1035,7 +1278,7 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1056,7 +1299,7 @@
       </c>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1077,7 +1320,7 @@
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
@@ -1098,7 +1341,7 @@
       </c>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>34</v>
       </c>
@@ -1119,7 +1362,7 @@
       </c>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
@@ -1140,7 +1383,7 @@
       </c>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>25</v>
       </c>
@@ -1161,7 +1404,7 @@
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -1182,7 +1425,7 @@
       </c>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -1211,24 +1454,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DC9D0E-3B70-4A1D-BCC4-A182A79A7BA4}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -1243,7 +1486,673 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="9">
+        <v>288931.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="2">
+        <v>73</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1276.5</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="9">
+        <v>149205.5</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.62931000000000004</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0.81932000000000005</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0.87922100000000003</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="2">
+        <v>43</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="2">
+        <v>281.5</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="9">
+        <v>20496.5</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="2">
+        <v>43</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="2">
+        <v>281.5</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="9">
+        <v>20496.5</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="11">
+        <v>0.875</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="11">
+        <v>0.79452100000000003</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="11">
+        <v>0.47226400000000002</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="11">
+        <v>3.6129000000000001E-2</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="2">
+        <v>20</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" s="9">
+        <v>18145.75</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="2">
+        <v>100</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" s="2">
+        <v>51.369900000000001</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" s="2">
+        <v>8.4268000000000001</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" s="2">
+        <v>7.7263999999999999</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
 </worksheet>
 </file>